--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -639,6 +639,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="F6" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J6" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -673,6 +673,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="F7" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J7" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -707,6 +707,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="F8" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J8" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -741,6 +741,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="F9" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J9" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -775,6 +775,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="F10" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J10" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -809,6 +809,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="F11" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J11" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -843,6 +843,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F12" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J12" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -877,6 +877,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F13" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J13" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -911,6 +911,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F14" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J14" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -945,6 +945,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F15" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J15" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -979,6 +979,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F16" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J16" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1013,6 +1013,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F17" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J17" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1047,6 +1047,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F18" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J18" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1081,6 +1081,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F19" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J19" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1115,6 +1115,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F20" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J20" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1149,6 +1149,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F21" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J21" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1183,6 +1183,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F22" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J22" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1217,6 +1217,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F23" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J23" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1251,6 +1251,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F24" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J24" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1285,6 +1285,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F25" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J25" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1319,6 +1319,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F26" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J26" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1353,6 +1353,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F27" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J27" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1387,6 +1387,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F28" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J28" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1421,6 +1421,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F29" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J29" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1455,6 +1455,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F30" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J30" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1489,6 +1489,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F31" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J31" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1523,6 +1523,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F32" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J32" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1557,6 +1557,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F33" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J33" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1591,6 +1591,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F34" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J34" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1625,6 +1625,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F35" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J35" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1659,6 +1659,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F36" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J36" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1693,6 +1693,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F37" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J37" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1727,6 +1727,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F38" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J38" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1761,6 +1761,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F39" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J39" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1795,6 +1795,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F40" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J40" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1829,6 +1829,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F41" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J41" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1863,6 +1863,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F42" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J42" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1897,6 +1897,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F43" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J43" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1931,6 +1931,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F44" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J44" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1965,6 +1965,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F45" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J45" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1999,6 +1999,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F46" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J46" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2033,6 +2033,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F47" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J47" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2067,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F48" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J48" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2101,6 +2101,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F49" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J49" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2135,6 +2135,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F50" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J50" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2169,6 +2169,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F51" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J51" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2203,6 +2203,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F52" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J52" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2237,6 +2237,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F53" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J53" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2271,6 +2271,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F54" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J54" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2305,6 +2305,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F55" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J55" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2339,6 +2339,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F56" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J56" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2373,6 +2373,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F57" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J57" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2407,6 +2407,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F58" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J58" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2441,6 +2441,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F59" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J59" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2475,6 +2475,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F60" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J60" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2509,6 +2509,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F61" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J61" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2543,6 +2543,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F62" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J62" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2577,6 +2577,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F63" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J63" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2611,6 +2611,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F64" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J64" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2645,6 +2645,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F65" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J65" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2679,6 +2679,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F66" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J66" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2713,6 +2713,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F67" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J67" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2747,6 +2747,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F68" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J68" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2781,6 +2781,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F69" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J69" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2815,6 +2815,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F70" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J70" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2849,6 +2849,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F71" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J71" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2883,6 +2883,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2917,6 +2917,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F73" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J73" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2951,6 +2951,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F74" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J74" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2985,6 +2985,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F75" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J75" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3019,6 +3019,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F76" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J76" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3053,6 +3053,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F77" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J77" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3087,6 +3087,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F78" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J78" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3121,6 +3121,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F79" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J79" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3155,6 +3155,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F80" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J80" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3189,6 +3189,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F81" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J81" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3223,6 +3223,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F82" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J82" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3257,6 +3257,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F83" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J83" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3291,6 +3291,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F84" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J84" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3325,6 +3325,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F85" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J85" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3359,6 +3359,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F86" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J86" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3393,6 +3393,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F87" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J87" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3427,6 +3427,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F88" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J88" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3461,6 +3461,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F89" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J89" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3495,6 +3495,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F90" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J90" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3529,6 +3529,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F91" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J91" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3563,6 +3563,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C92" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D92" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E92" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F92" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G92" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H92" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I92" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J92" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3597,6 +3597,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C93" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D93" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E93" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F93" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G93" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H93" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I93" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J93" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3631,6 +3631,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C94" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D94" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E94" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F94" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G94" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H94" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I94" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J94" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
